--- a/www/ig/fhir/sdo/StructureDefinition-esms-consent.xlsx
+++ b/www/ig/fhir/sdo/StructureDefinition-esms-consent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>4.0.6</t>
+    <t>4.0.7</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-15T14:22:03+00:00</t>
+    <t>2026-06-29T08:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
@@ -436,7 +436,7 @@
     <t>Consent.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -474,7 +474,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -498,7 +498,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -541,7 +541,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -715,7 +715,7 @@
     <t>The four anticipated uses for the Consent Resource.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-scope</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-scope|4.0.1</t>
   </si>
   <si>
     <t>Consent.category</t>
@@ -738,7 +738,7 @@
     <t>A classification of the type of consents found in a consent statement.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-category</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-category|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -756,7 +756,7 @@
     <t>Consent.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Reference(Patient|4.0.1)
 </t>
   </si>
   <si>
@@ -813,7 +813,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|Patient|Practitioner|RelatedPerson|PractitionerRole)
+    <t xml:space="preserve">Reference(Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|RelatedPerson|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -842,7 +842,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -859,7 +859,7 @@
   </si>
   <si>
     <t>Attachment
-Reference(Consent|DocumentReference|Contract|QuestionnaireResponse)</t>
+Reference(Consent|4.0.1|DocumentReference|4.0.1|Contract|4.0.1|QuestionnaireResponse|4.0.1)</t>
   </si>
   <si>
     <t>Source from which this consent is taken</t>
@@ -950,7 +950,7 @@
     <t>Regulatory policy examples.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-policy</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-policy|4.0.1</t>
   </si>
   <si>
     <t>Consent.verification</t>
@@ -987,7 +987,7 @@
     <t>Consent.verification.verifiedWith</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1085,13 +1085,13 @@
     <t>How an actor is involved in the consent considerations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-role-type</t>
+    <t>http://hl7.org/fhir/ValueSet/security-role-type|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.actor.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|Group|CareTeam|Organization|Patient|Practitioner|RelatedPerson|PractitionerRole)
+    <t xml:space="preserve">Reference(Device|4.0.1|Group|4.0.1|CareTeam|4.0.1|Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|RelatedPerson|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1119,7 +1119,7 @@
     <t>Detailed codes for the consent action.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-action</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-action|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.securityLabel</t>
@@ -1167,7 +1167,7 @@
     <t>The class (type) of information a consent rule covers.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-content-class</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-content-class|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.code</t>
@@ -1185,7 +1185,7 @@
     <t>If this code is found in an instance, then the exception applies.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-content-code</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-content-code|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.dataPeriod</t>
@@ -1293,7 +1293,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1374,7 +1374,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1797,17 +1797,17 @@
   <dimension ref="A1:AN80"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="50.02734375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="50.02734375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.890625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.890625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="94.234375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="117.01953125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1816,26 +1816,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="55.12890625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="125.95703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.5703125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="47.265625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="107.984375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="45.0703125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="46.4453125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="102.6171875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="39.8203125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="87.9765625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
